--- a/docs/Nakshatra_2026_Technical_Test_Checklist.xlsx
+++ b/docs/Nakshatra_2026_Technical_Test_Checklist.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Guide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Test Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Execution Guide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Coverage Map" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Checklist'!$A$1:$K$70</definedName>
@@ -72,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -85,6 +86,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -464,7 +468,10 @@
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,6 +530,21 @@
           <t>Test Date</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Automation Type</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage Refs</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -557,13 +579,35 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,13 +642,35 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>A-07; J-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -639,13 +705,35 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>A-05</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -680,13 +768,40 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>A-09</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>SESSION_INVALID envelope returns user to the login card.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -721,13 +836,40 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>A-08</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>502 envelope: session kept, warning shown, next sign-in recovers.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -762,13 +904,40 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>J-01</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Backend logout called; sessionStorage cleared; login shown.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -809,7 +978,17 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Needs two browser profiles; manual multi-tab/profile check.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -844,13 +1023,40 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>UI gating + forbidden-URL redirect verified across roles; backend enforcement of archive/user-management still needs a live retest.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -885,13 +1091,35 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -926,13 +1154,40 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>B-05</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Only missing fields prompt; found fields kept.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -967,13 +1222,40 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Caretaker listed separately; official contact input left empty with warning.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1008,13 +1290,35 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1049,13 +1353,40 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Connected-but-sync-failed outcome with backend reason + Retry.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1090,13 +1421,40 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Exactly 1 connect + 1 sync request asserted; no duplicate home.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1131,13 +1489,40 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ALREADY_CONNECTED outcome; no duplicate card.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1172,13 +1557,35 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1213,13 +1620,40 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>B-06; B-07</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Inaccessible-sheet error and non-JSON/404 responses verified; typing a malformed URL is blocked by the browser input (manual variant).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1254,13 +1688,28 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Requires a real Sheets sync round-trip changing backend contact values.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1295,13 +1744,40 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>C-06</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>HTML 404 page: could-not-confirm outcome, technical detail preserved, never success.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1342,7 +1818,17 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>DevTools inspection against the deployed backend.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1377,13 +1863,40 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Terminal error state + working retry verified (dashboard summary, attendance read); slow-network timing variant remains manual.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1418,13 +1931,35 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
+          <t>Pass (live)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Live probe vs production /exec (2026-10-12): POST {"action":"validateSession"} without sessionId -&gt; HTTP 200 structured envelope success:false, error.code=SESSION_REQUIRED; no sensitive data returned; round-trip 2.55s. See docs/acceptance-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>QA lead (live probe)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Only this single read-only action was probed live (no credentials, no writes). Previous status: Not Run (2026-10-12 baseline). Full action-contract verification against the deployed backend remains Not Run (COMP-001).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1459,13 +1994,23 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Real two-way Sheets write-back needs a disposable non-production backend + test spreadsheet (unavailable).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1500,13 +2045,23 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Real write-back to the participant sheet; unsafe against production.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1541,13 +2096,23 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Real rename write-back + Event-wise sheet update.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1582,13 +2147,23 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Depends on a real rename round-trip.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1623,13 +2198,23 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Verdict strings are unit-pinned (164 vitest tests); live write-back failure needs a real backend.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1664,13 +2249,23 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Needs real partial-failure reconciliation.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1705,13 +2300,23 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Multi-home job lifecycle needs a real backend + multiple test homes.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1746,13 +2351,23 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Needs a real repeated sync round-trip.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1787,13 +2402,23 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Trigger-based flow only exists in a deployed spreadsheet.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1828,13 +2453,40 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>J-03</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Page render + participant/home mapping verified with stub data; live source-workbook comparison pending.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1875,7 +2527,17 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Candidate for a mocked E2E journey.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1916,7 +2578,22 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>J-03</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Mockable with a getParticipantEventSummaries stub.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1957,7 +2634,12 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1998,7 +2680,12 @@
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2039,7 +2726,12 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2080,7 +2772,17 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>VERSION_CONFLICT pattern already proven for attendance (ATT-006).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2115,13 +2817,35 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Catalogue listing verified in stubbed E2E; live master-list comparison pending.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2162,7 +2886,12 @@
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2203,7 +2932,22 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Needs archived-home roster semantics (live or richer stub).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2238,13 +2982,35 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2279,13 +3045,35 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2320,13 +3108,40 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Persistence re-verified via forced re-read after retry; literal F5 step is manual.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2361,13 +3176,35 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2402,13 +3239,40 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>expectedVersion enforced by the stub; version increment asserted indirectly.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2443,13 +3307,40 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Conflict message shown, latest value reloaded, buttons usable again.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2484,13 +3375,40 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>F-07; E-04</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Backend rejection surfaced verbatim; nothing marked.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2531,7 +3449,12 @@
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2572,7 +3495,12 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2613,7 +3541,12 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2654,7 +3587,12 @@
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2695,7 +3633,12 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2736,7 +3679,12 @@
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2777,7 +3725,12 @@
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2818,7 +3771,22 @@
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Reports page renders in the responsive sweep; data comparison not run.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2853,13 +3821,35 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2894,13 +3884,35 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2935,13 +3947,40 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>E-05</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Verified restoring from the zero-active-homes state (rendering defect fixed).</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2976,13 +4015,23 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Retest</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Automated (unit)</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>UI gate unit-covered (canArchive); E2E non-admin archive attempt + backend rejection pending.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3023,7 +4072,22 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>I-01</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Needs listUsers/approveUser stubs in the E2E backend router.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3064,7 +4128,17 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Duplicate requests partly disproven by stub request counting (HOME-006).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3099,13 +4173,40 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
+          <t>Retest</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>H-01; H-02</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Dashboard/homes/participants/attendance terminal states verified; remaining pages pending.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3146,7 +4247,17 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Duplicate prevention partly proven by HOME-006/ATT-004 mocked journeys.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3187,7 +4298,12 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3228,7 +4344,12 @@
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3269,7 +4390,17 @@
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Review step before any live execution.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3310,7 +4441,17 @@
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Live observation 2026-10-12: one well-formed POST returned a proper JSON envelope (structured error); full contract comparison still pending.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3351,7 +4492,1912 @@
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-009</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in success only after backend confirms</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Sign in and observe the UI before the verification request resolves; then force a failure.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Sign-in success appears only after APPROVED + valid session; a failure is never shown as success.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-010</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>No app shell behind the login card (unauthenticated)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Sign out and open the app root.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Only the login page renders - no sidebar/header/footer around it.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>A-04</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-011</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Refresh on #/login with a valid session</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Sign in, navigate to #/login manually, press F5.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Startup validation recovers the session and lands on /dashboard; the shell never wraps the login card.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>A-06</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Covers the session-restore race fixed in app.ts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-012</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Unregistered Google account</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Sign in with a valid Google identity that is not registered.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Honest NOT_REGISTERED panel; no session stored; no crash.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>A-10</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-013</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Identity-recovery login for a recovered user</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Run runIdentityRecoveryCheck for the recovered account, then sign in live.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Recovered user signs in and receives the correct role.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>A-11</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Needs the Apps Script recovery routine + the real account (production data). Still pending on the user side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-014</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Role-filtered navigation and settings gating</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Sign in as ADMIN and as CERTIFICATE_TEAM; inspect navigation, open #/settings directly as non-admin.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Each role sees only its permitted sections; #/settings is hidden and redirects non-admins to the dashboard.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>A-12; A-13</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>HOME-011</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Preview gated on a spreadsheet URL</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Open Add shelter home; observe Connect button before/after entering a URL.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Preview/Connect stays disabled until a URL is entered.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>HOME-012</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Explicit caretaker contact prefills Contact Name</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Preview a workbook whose metadata contains an explicit official contact.</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>The Contact Name input is prefilled from the explicit metadata (never from caretaker data).</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>HOME-013</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Malformed URL client-side error</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Type a syntactically invalid URL bypassing browser validation (e.g. via JS) and preview.</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Client-side validation message; no request issued.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Manual (mocked)</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>B-06</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>The browser URL input normally blocks typing nonsense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>HOME-014</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Spreadsheet ID never exposed in the UI</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Complete a connect and inspect the page body for the raw spreadsheet id.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>The identifier is not shown anywhere in the user interface.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>HOME-015</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous connect failure re-checks the homes list</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Force the connect request to fail ambiguously (504/HTML) while the connection actually persisted.</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>The verification re-read finds the persisted home and reports ALREADY_CONNECTED; no false failure.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>C-07</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>HOME-016</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Friendly sync status labels (no raw codes)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Open the homes list with homes in different sync states.</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Human-readable labels (e.g. Synced / Sync needed); raw backend codes appear only in diagnostics.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>API-005</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>API/Transport</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Technical detail only in diagnostics</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Trigger backend failures on connect/preview/sync journeys.</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Primary messages stay human-readable; raw codes/statuses appear only in the diagnostics detail line.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Verified for the connect/preview failure surfaces; other surfaces manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>API-006</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>API/Transport</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Unknown/unmocked action is aborted, never faked</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Call a frontend journey whose backend action is not registered in the test stub router.</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>The request is aborted at the network layer; the UI shows an honest empty/error state; the session is kept; no fabricated data.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Guards the E2E suite itself against leaking to production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ATT-008</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Failed read shows error with a working Retry</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Force listAttendance to fail; press Retry with the backend recovered.</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Error replaces content honestly; Retry issues a real new request and recovers the saved marks.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ATT-009</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Failed save never reports success</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Abort/mark-fail the save request for an attendance row.</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Error is shown, no success message appears, the row returns to idle and can be retried.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>IMPORT-001</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Imports</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Initial import summary is truthful</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Connect a test workbook and read the import outcome.</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>initialImport attempted/status/counts reflect the backend response exactly; no invented numbers.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ADMIN-006</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>History preserved after archiving</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Archive a test home with historical attendance/scores and inspect past records.</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Historical records remain intact and attributable; nothing is deleted by archiving.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Blocked (live backend)</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>E-06</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Requires real historical records; a stub can only re-assert itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>A11Y-001</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>axe smoke: no critical/serious violations on key routes</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Run axe-core on login, dashboard, homes, participants, events, attendance (desktop).</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Zero critical/serious violations. Found issues (aria-hidden focus, prohibited labels, name mismatch, unnamed selects, contrast) were fixed 2026-10-12.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Smoke signal only - not a WCAG compliance statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>A11Y-002</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Keyboard-only navigation</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Traverse login and each main page using keyboard only.</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>All interactive controls reachable and operable; visible focus; no traps.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="n"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Manual (mocked)</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>A11Y-003</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Screen-reader spot check</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Spot-check key flows with a screen reader (NVDA/VoiceOver).</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Names, roles and states announced correctly for nav, tables, dialogs and toasts.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="n"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SEC-001</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Credential/token hygiene</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Inspect sessionStorage, network payloads and logs during sign-in/out and API errors.</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Session id stored only in sessionStorage; no tokens/secrets logged or rendered; session cleared on logout.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Session-clear on logout verified; full secret-hygiene sweep manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SEC-002</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>XSS resistance of rendered data</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Import/register test values containing HTML/script metacharacters; view them in lists/tables.</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Values render as text; no script execution or HTML injection.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="n"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Not automated (mockable)</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>RESP-001</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>No horizontal overflow on key routes</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Sweep login/dashboard/homes/participants/events/attendance at desktop, tablet and mobile viewports.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>No horizontal scrolling or clipped content at any emulated viewport.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Emulated Chromium viewports (1280 / 768x1024 touch / Pixel 7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>RESP-002</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Mobile navigation drawer</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Open the app at mobile width; open the drawer and navigate to a section.</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Drawer opens from the header menu button; navigation works; drawer closes after navigation.</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>COMP-003</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Desktop Chromium E2E pass</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Run the full Playwright suite on the desktop project.</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>All mocked journeys pass (2026-10-12: 44 journeys x 3 projects, 0 failures).</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>COMP-004</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Mobile emulation pass (Pixel 7)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Run the suite on the mobile-chromium project.</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>All applicable journeys pass; drawer/nav assertions viewport-aware.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>COMP-005</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Tablet emulation pass (768x1024 touch)</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Run the suite on the tablet-chromium project.</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>All applicable journeys pass at tablet size with touch enabled.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>COMP-006</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Real device validation</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Smoke-test sign-in, dashboard, attendance and a sync read on physical Android + iOS devices/browsers.</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Layouts and touch interactions hold on real devices; no emulation-only artifacts.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="n"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Emulation is not real-device testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>DATA-005</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Failed read honesty (no fabricated or stale-as-current data)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Force dashboard/homes/participants reads to fail; observe the page; then retry.</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Content is replaced with an honest error + Retry (established design); nothing is fabricated or blanked; session is kept; retry recovers.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E suite (desktop/tablet/mobile Chromium), 2026-10-12 - e2e/journeys/*.spec.ts; see docs/qa-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Automated (Playwright)</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Automated (mocked E2E)</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SEC-003</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Unauthenticated GET does not expose production metadata</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Send a plain GET to the deployed /exec endpoint with no session and inspect the response.</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>No production spreadsheet metadata (name/sheet structure) is returned without a valid session.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Live GET (2026-10-12, 3.4s): HTTP 200 application/json success:true including the real production spreadsheet name and its sheet names with row/column counts. Confirmed by Code.gs doGet() (line 126): no session check; opens SOURCE_SPREADSHEET_ID and returns metadata. See docs/acceptance-report-2026-10-12.md</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>DEF-001</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>QA lead (live probe)</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Manual (live)</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>X-03</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>HIGH severity unauthorized information-disclosure path (no participant PII observed in the response - metadata only). Backend fix required in Code.gs (out of frontend scope): gate doGet to a valid session or return no metadata; then redeploy and re-run this probe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K70"/>
@@ -3365,7 +6411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3378,7 +6424,6 @@
           <t>Nakshatra 2026 — Technical Test Execution Guide</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3412,7 +6457,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Not Run | Pass | Fail | Blocked | Retest</t>
+          <t>Not Run | Pass | Fail | Blocked | Retest | Pass (mocked) | Pass (live)</t>
         </is>
       </c>
     </row>
@@ -3497,6 +6542,90 @@
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Record actual result, evidence, defect ID, tester and test date for each executed case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>The case was executed successfully in the stubbed E2E environment (local dev server + intercepted backend, Chromium desktop/tablet/mobile emulation) on 2026-10-12. The live deployment still needs final acceptance before marking plain Pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Automation Type</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Values: Automated (mocked E2E) = Playwright journey with stubbed backend; Automated (unit) = vitest; Manual (live) = human test against the deployed backend; Manual (mocked) = human test in the stubbed environment; Not automated (mockable) = candidate for future E2E automation; Blocked (live backend) = impossible today without real Apps Script/Sheets/OAuth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Mocked vs live</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mocked E2E proves frontend behavior and error honesty, not deployed Apps Script contracts, real Google sign-in, real Sheets read/write, triggers or concurrent multi-user writes. Live results require a disposable test spreadsheet + test home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Desktop / mobile</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Responsive checks ran as Chromium emulation: desktop 1280px, tablet 768x1024 (touch) and mobile Pixel 7. Emulation is not real-device testing - validate once on physical Android/iOS devices before release (COMP-006).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Safe test data</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Use a disposable test home and a disposable Google Sheet with synthetic data (fixture data uses example.com). Never bulk-delete production data, never run destructive writes against production, and record no tokens/secrets/session credentials in evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Coverage map</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>The 'Coverage Map' sheet traces every requirement in docs/manual-test-checklist-2026-10-12.csv (A-01..J-03) plus extra areas (security, accessibility, responsive) to one or more Test IDs with verification status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Pass (live)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>The case was executed successfully against the designated NON-PRODUCTION backend with real dependencies. Today only credential-free, read-only probes against the production endpoint were safe; they are recorded explicitly as live probes, never as full live acceptance.</t>
         </is>
       </c>
     </row>
@@ -3506,4 +6635,2326 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Requirement / coverage statement</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Test Case ID(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Approved sign-in redirects to dashboard</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AUTH-001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Success shown only after backend confirms</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AUTH-009</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Login card disappears after navigation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AUTH-001; AUTH-010</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>No app shell behind login card</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AUTH-010</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Session survives refresh (8h validity)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AUTH-003</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Refresh on #/login with valid session</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AUTH-011</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Open #/login while signed in</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AUTH-002</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Transient network failure keeps session</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AUTH-005</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Invalid session returns to login</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AUTH-004</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Unregistered Google account handled honestly</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AUTH-012</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sign-in</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Identity-recovery login for recovered user</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AUTH-013</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ADMIN sees all sections</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AUTH-014</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Limited role sees only permitted sections</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AUTH-014</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ADMIN-only actions gated</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AUTH-008; ADMIN-004</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pass (mocked) | Retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Preview requires a valid URL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HOME-011</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Detected metadata values display</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HOME-001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Caretaker contact never the official contact</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HOME-003</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Explicit contact prefilled</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HOME-012</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B-05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Only missing fields prompt</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HOME-002</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Invalid URL error</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HOME-009; HOME-013</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Not Run | Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B-07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Inaccessible sheet error</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HOME-009</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Shelter Homes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No spreadsheet id exposed</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HOME-014</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Connect &amp; import</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fresh connect succeeds</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HOME-004; IMPORT-001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Connect &amp; import</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Connect success + import failure distinct</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HOME-005</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Connect &amp; import</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Retry sync reuses identity, no duplicates</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HOME-006</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Connect &amp; import</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Already-connected active source</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HOME-007</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Connect &amp; import</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Archived source handled</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HOME-008</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>API errors</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HTTP 404 / non-JSON never success</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>API-001</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C-07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Connect &amp; import</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ambiguous failure re-checks homes</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HOME-015</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Status display</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Friendly status labels, no raw codes</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HOME-016</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Status display</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Contact updates without full refresh</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HOME-010</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Status display</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Technical detail stays in diagnostics</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>API-005</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Archive impact preview truthful</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ADMIN-001</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Archive removes home from active list</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ADMIN-002</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Archived participants leave rosters</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EVENT-003</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>E-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Protected writes rejected clearly</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ATT-007</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>E-05</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Restore returns the home</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ADMIN-003</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>E-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>History preserved after archive</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ADMIN-006</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Saved attendance displays on load</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ATT-001</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mark persists and survives refresh</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ATT-002; ATT-003</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Idempotent identical re-save</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ATT-004</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Update uses expectedVersion</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ATT-005</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VERSION_CONFLICT recovery</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ATT-006</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Failed save never shows success</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ATT-009</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Archived/ineligible backend rejection</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ATT-007</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sync All</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Job starts with real id and progress</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SYNC-007</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sync All</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>No duplicate job on refresh</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SYNC-007</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sync All</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Accurate counts</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SYNC-007</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sync All</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Archived homes excluded</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SYNC-007</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>G-05</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sync All</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cache updated after completion</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SYNC-007</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Retry buttons issue real new requests</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>API-003; ATT-008</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Existing data stays visible / honest on refresh</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DATA-005</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>No duplicate or stale requests</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PERF-001; API-002</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>I-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>User management (ADMIN)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ADMIN-005</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Reports load with real data</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>REPORT-001</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>J-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Login / RBAC / logout intact</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AUTH-002; AUTH-006</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>J-02</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Rename sheet-sync verdicts truthful</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SYNC-005</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>J-03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Participant summaries correct</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PART-001; PART-003</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Not Run | Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>X-01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Two-way sync</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sheet -&gt; app participant sync</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SYNC-001; SYNC-008; SYNC-009</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>X-02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Two-way sync</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>App -&gt; sheet write-back and rename</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SYNC-002; SYNC-003; SYNC-004; DATA-002</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Blocked | Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>X-03</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Unauthenticated API access rejected</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>API-004; SEC-003</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Fail | Pass (live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>X-04</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Credential/token hygiene</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SEC-001</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>X-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>XSS resistance of rendered data</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SEC-002</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>X-06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Automated axe smoke on key routes</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>A11Y-001</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>X-07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Keyboard-only navigation</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>A11Y-002</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>X-08</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Screen-reader spot check</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>A11Y-003</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>X-09</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>No horizontal overflow (desktop/tablet/mobile)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>RESP-001</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>X-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Mobile navigation drawer</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RESP-002</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>X-11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Browsers</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Desktop Chromium E2E pass</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>COMP-003</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>X-12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Browsers</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Mobile emulation pass</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>COMP-004</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>X-13</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Browsers</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tablet emulation pass</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>COMP-005</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>X-14</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Browsers</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Real device validation</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>COMP-006</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>X-15</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Multi-user simultaneous writes</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>COMP-002; PART-007; ATT-006; SCORE-002</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Not Run | Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>X-16</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Request fan-out / N+1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PERF-001</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>X-17</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Loading terminal states</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PERF-002</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>X-18</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Data integrity</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Duplicate prevention across operations</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DATA-001</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>X-19</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Data integrity</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Audit history</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DATA-003</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>X-20</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Data integrity</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Production safety</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DATA-004</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>X-21</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Backend contract</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Schema/routes match frontend actions</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>COMP-001</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>X-22</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Score persistence &amp; conflicts</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SCORE-001; SCORE-002; SCORE-003</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>X-23</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Teams</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Team membership persistence &amp; gates</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TEAM-001; TEAM-002</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>X-24</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Results consistency with scores</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>RESULT-001</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>X-25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Certificates</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Certificate flow</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CERT-001</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>X-26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Event master &amp; rosters</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EVENT-001; EVENT-002; EVENT-003</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Not Run | Pass (mocked)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>